--- a/Team-Data/2013-14/11-14-2013-14.xlsx
+++ b/Team-Data/2013-14/11-14-2013-14.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,7 +806,7 @@
         <v>1.8</v>
       </c>
       <c r="AD2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AE2" t="n">
         <v>13</v>
@@ -760,7 +827,7 @@
         <v>17</v>
       </c>
       <c r="AK2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AL2" t="n">
         <v>12</v>
@@ -778,13 +845,13 @@
         <v>12</v>
       </c>
       <c r="AQ2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AR2" t="n">
         <v>29</v>
       </c>
       <c r="AS2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AT2" t="n">
         <v>21</v>
@@ -796,10 +863,10 @@
         <v>3</v>
       </c>
       <c r="AW2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AX2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AY2" t="n">
         <v>6</v>
@@ -811,7 +878,7 @@
         <v>10</v>
       </c>
       <c r="BB2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BC2" t="n">
         <v>11</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>11-14-2013-14</t>
+          <t>2013-11-14</t>
         </is>
       </c>
     </row>
@@ -921,13 +988,13 @@
         <v>-0.9</v>
       </c>
       <c r="AD3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE3" t="n">
         <v>13</v>
       </c>
       <c r="AF3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AG3" t="n">
         <v>16</v>
@@ -936,10 +1003,10 @@
         <v>12</v>
       </c>
       <c r="AI3" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AJ3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK3" t="n">
         <v>12</v>
@@ -957,7 +1024,7 @@
         <v>20</v>
       </c>
       <c r="AP3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ3" t="n">
         <v>10</v>
@@ -993,7 +1060,7 @@
         <v>20</v>
       </c>
       <c r="BB3" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BC3" t="n">
         <v>17</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>11-14-2013-14</t>
+          <t>2013-11-14</t>
         </is>
       </c>
     </row>
@@ -1103,13 +1170,13 @@
         <v>-5.4</v>
       </c>
       <c r="AD4" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AE4" t="n">
         <v>25</v>
       </c>
       <c r="AF4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AG4" t="n">
         <v>25</v>
@@ -1121,7 +1188,7 @@
         <v>22</v>
       </c>
       <c r="AJ4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AK4" t="n">
         <v>17</v>
@@ -1148,10 +1215,10 @@
         <v>25</v>
       </c>
       <c r="AS4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AT4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AU4" t="n">
         <v>16</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>11-14-2013-14</t>
+          <t>2013-11-14</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1352,7 @@
         <v>-4.3</v>
       </c>
       <c r="AD5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AE5" t="n">
         <v>13</v>
@@ -1303,7 +1370,7 @@
         <v>30</v>
       </c>
       <c r="AJ5" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AK5" t="n">
         <v>29</v>
@@ -1324,7 +1391,7 @@
         <v>2</v>
       </c>
       <c r="AQ5" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AR5" t="n">
         <v>17</v>
@@ -1345,7 +1412,7 @@
         <v>26</v>
       </c>
       <c r="AX5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AY5" t="n">
         <v>20</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>11-14-2013-14</t>
+          <t>2013-11-14</t>
         </is>
       </c>
     </row>
@@ -1473,7 +1540,7 @@
         <v>19</v>
       </c>
       <c r="AF6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG6" t="n">
         <v>13</v>
@@ -1485,10 +1552,10 @@
         <v>27</v>
       </c>
       <c r="AJ6" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AK6" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL6" t="n">
         <v>29</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>11-14-2013-14</t>
+          <t>2013-11-14</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1716,7 @@
         <v>-8.699999999999999</v>
       </c>
       <c r="AD7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE7" t="n">
         <v>19</v>
@@ -1685,7 +1752,7 @@
         <v>22</v>
       </c>
       <c r="AP7" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ7" t="n">
         <v>13</v>
@@ -1697,7 +1764,7 @@
         <v>19</v>
       </c>
       <c r="AT7" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AU7" t="n">
         <v>25</v>
@@ -1706,7 +1773,7 @@
         <v>14</v>
       </c>
       <c r="AW7" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AX7" t="n">
         <v>14</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>11-14-2013-14</t>
+          <t>2013-11-14</t>
         </is>
       </c>
     </row>
@@ -1831,13 +1898,13 @@
         <v>3.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AE8" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AF8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG8" t="n">
         <v>7</v>
@@ -1846,7 +1913,7 @@
         <v>12</v>
       </c>
       <c r="AI8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AJ8" t="n">
         <v>7</v>
@@ -1879,7 +1946,7 @@
         <v>16</v>
       </c>
       <c r="AT8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AU8" t="n">
         <v>11</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>11-14-2013-14</t>
+          <t>2013-11-14</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2080,7 @@
         <v>-0.4</v>
       </c>
       <c r="AD9" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AE9" t="n">
         <v>19</v>
@@ -2058,7 +2125,7 @@
         <v>4</v>
       </c>
       <c r="AS9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AT9" t="n">
         <v>2</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>11-14-2013-14</t>
+          <t>2013-11-14</t>
         </is>
       </c>
     </row>
@@ -2195,13 +2262,13 @@
         <v>-3.3</v>
       </c>
       <c r="AD10" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AE10" t="n">
         <v>25</v>
       </c>
       <c r="AF10" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AG10" t="n">
         <v>25</v>
@@ -2216,10 +2283,10 @@
         <v>8</v>
       </c>
       <c r="AK10" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AL10" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AM10" t="n">
         <v>15</v>
@@ -2261,7 +2328,7 @@
         <v>14</v>
       </c>
       <c r="AZ10" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BA10" t="n">
         <v>11</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>11-14-2013-14</t>
+          <t>2013-11-14</t>
         </is>
       </c>
     </row>
@@ -2299,103 +2366,103 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F11" t="n">
         <v>3</v>
       </c>
       <c r="G11" t="n">
-        <v>0.667</v>
+        <v>0.625</v>
       </c>
       <c r="H11" t="n">
         <v>48</v>
       </c>
       <c r="I11" t="n">
-        <v>39.7</v>
+        <v>39</v>
       </c>
       <c r="J11" t="n">
-        <v>80.8</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="K11" t="n">
-        <v>0.491</v>
+        <v>0.493</v>
       </c>
       <c r="L11" t="n">
-        <v>11.2</v>
+        <v>10.9</v>
       </c>
       <c r="M11" t="n">
-        <v>24.7</v>
+        <v>24.9</v>
       </c>
       <c r="N11" t="n">
-        <v>0.455</v>
+        <v>0.437</v>
       </c>
       <c r="O11" t="n">
-        <v>14.7</v>
+        <v>15</v>
       </c>
       <c r="P11" t="n">
-        <v>20.4</v>
+        <v>21.3</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.717</v>
+        <v>0.706</v>
       </c>
       <c r="R11" t="n">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="S11" t="n">
-        <v>33.6</v>
+        <v>35</v>
       </c>
       <c r="T11" t="n">
-        <v>42.2</v>
+        <v>43.6</v>
       </c>
       <c r="U11" t="n">
+        <v>25</v>
+      </c>
+      <c r="V11" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="W11" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="X11" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Z11" t="n">
         <v>25.1</v>
       </c>
-      <c r="V11" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="W11" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="X11" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>24.8</v>
-      </c>
       <c r="AA11" t="n">
-        <v>21.1</v>
+        <v>21.6</v>
       </c>
       <c r="AB11" t="n">
-        <v>105.2</v>
+        <v>103.9</v>
       </c>
       <c r="AC11" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG11" t="n">
         <v>7</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>3</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>3</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>4</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>4</v>
       </c>
       <c r="AH11" t="n">
         <v>12</v>
       </c>
       <c r="AI11" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AJ11" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="AK11" t="n">
         <v>2</v>
@@ -2407,34 +2474,34 @@
         <v>5</v>
       </c>
       <c r="AN11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO11" t="n">
+        <v>26</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>22</v>
+      </c>
+      <c r="AQ11" t="n">
         <v>27</v>
       </c>
-      <c r="AP11" t="n">
-        <v>27</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>22</v>
-      </c>
       <c r="AR11" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AS11" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="AT11" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="AU11" t="n">
         <v>5</v>
       </c>
       <c r="AV11" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AW11" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AX11" t="n">
         <v>5</v>
@@ -2443,10 +2510,10 @@
         <v>4</v>
       </c>
       <c r="AZ11" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BA11" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BB11" t="n">
         <v>7</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>11-14-2013-14</t>
+          <t>2013-11-14</t>
         </is>
       </c>
     </row>
@@ -2481,88 +2548,88 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F12" t="n">
         <v>4</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6</v>
+        <v>0.556</v>
       </c>
       <c r="H12" t="n">
-        <v>49.5</v>
+        <v>49.7</v>
       </c>
       <c r="I12" t="n">
-        <v>36.1</v>
+        <v>36.7</v>
       </c>
       <c r="J12" t="n">
-        <v>77.59999999999999</v>
+        <v>78.7</v>
       </c>
       <c r="K12" t="n">
-        <v>0.465</v>
+        <v>0.466</v>
       </c>
       <c r="L12" t="n">
         <v>8.699999999999999</v>
       </c>
       <c r="M12" t="n">
-        <v>27.1</v>
+        <v>27</v>
       </c>
       <c r="N12" t="n">
         <v>0.321</v>
       </c>
       <c r="O12" t="n">
-        <v>26.6</v>
+        <v>25.3</v>
       </c>
       <c r="P12" t="n">
-        <v>38.2</v>
+        <v>37.6</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.696</v>
+        <v>0.675</v>
       </c>
       <c r="R12" t="n">
         <v>11.4</v>
       </c>
       <c r="S12" t="n">
-        <v>36.2</v>
+        <v>36.7</v>
       </c>
       <c r="T12" t="n">
-        <v>47.6</v>
+        <v>48.1</v>
       </c>
       <c r="U12" t="n">
-        <v>19.5</v>
+        <v>20.1</v>
       </c>
       <c r="V12" t="n">
-        <v>19.4</v>
+        <v>19.6</v>
       </c>
       <c r="W12" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="X12" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="Y12" t="n">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="Z12" t="n">
-        <v>22.4</v>
+        <v>22.8</v>
       </c>
       <c r="AA12" t="n">
-        <v>29.3</v>
+        <v>29.4</v>
       </c>
       <c r="AB12" t="n">
-        <v>107.5</v>
+        <v>107.3</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AD12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AF12" t="n">
         <v>12</v>
@@ -2571,16 +2638,16 @@
         <v>11</v>
       </c>
       <c r="AH12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AI12" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AJ12" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AK12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AL12" t="n">
         <v>7</v>
@@ -2598,7 +2665,7 @@
         <v>1</v>
       </c>
       <c r="AQ12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AR12" t="n">
         <v>16</v>
@@ -2610,22 +2677,22 @@
         <v>1</v>
       </c>
       <c r="AU12" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AV12" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AW12" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AX12" t="n">
         <v>2</v>
       </c>
       <c r="AY12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AZ12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BA12" t="n">
         <v>1</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>11-14-2013-14</t>
+          <t>2013-11-14</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2808,7 @@
         <v>10.4</v>
       </c>
       <c r="AD13" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AE13" t="n">
         <v>1</v>
@@ -2786,7 +2853,7 @@
         <v>23</v>
       </c>
       <c r="AS13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AT13" t="n">
         <v>10</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>11-14-2013-14</t>
+          <t>2013-11-14</t>
         </is>
       </c>
     </row>
@@ -2923,16 +2990,16 @@
         <v>4</v>
       </c>
       <c r="AD14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE14" t="n">
         <v>3</v>
       </c>
       <c r="AF14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AH14" t="n">
         <v>12</v>
@@ -2950,10 +3017,10 @@
         <v>10</v>
       </c>
       <c r="AM14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AN14" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AO14" t="n">
         <v>5</v>
@@ -2971,7 +3038,7 @@
         <v>17</v>
       </c>
       <c r="AT14" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AU14" t="n">
         <v>3</v>
@@ -2989,7 +3056,7 @@
         <v>5</v>
       </c>
       <c r="AZ14" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BA14" t="n">
         <v>2</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>11-14-2013-14</t>
+          <t>2013-11-14</t>
         </is>
       </c>
     </row>
@@ -3114,13 +3181,13 @@
         <v>26</v>
       </c>
       <c r="AG15" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AH15" t="n">
         <v>12</v>
       </c>
       <c r="AI15" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AJ15" t="n">
         <v>3</v>
@@ -3132,7 +3199,7 @@
         <v>3</v>
       </c>
       <c r="AM15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AN15" t="n">
         <v>7</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>11-14-2013-14</t>
+          <t>2013-11-14</t>
         </is>
       </c>
     </row>
@@ -3287,25 +3354,25 @@
         <v>-4.8</v>
       </c>
       <c r="AD16" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AE16" t="n">
         <v>19</v>
       </c>
       <c r="AF16" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AG16" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AH16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AI16" t="n">
         <v>16</v>
       </c>
       <c r="AJ16" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AK16" t="n">
         <v>7</v>
@@ -3323,7 +3390,7 @@
         <v>20</v>
       </c>
       <c r="AP16" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ16" t="n">
         <v>10</v>
@@ -3356,10 +3423,10 @@
         <v>16</v>
       </c>
       <c r="BA16" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BB16" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BC16" t="n">
         <v>25</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>11-14-2013-14</t>
+          <t>2013-11-14</t>
         </is>
       </c>
     </row>
@@ -3469,13 +3536,13 @@
         <v>6.6</v>
       </c>
       <c r="AD17" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AE17" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AF17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG17" t="n">
         <v>7</v>
@@ -3484,7 +3551,7 @@
         <v>12</v>
       </c>
       <c r="AI17" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AJ17" t="n">
         <v>30</v>
@@ -3499,7 +3566,7 @@
         <v>14</v>
       </c>
       <c r="AN17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO17" t="n">
         <v>12</v>
@@ -3508,7 +3575,7 @@
         <v>8</v>
       </c>
       <c r="AQ17" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AR17" t="n">
         <v>30</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>11-14-2013-14</t>
+          <t>2013-11-14</t>
         </is>
       </c>
     </row>
@@ -3651,13 +3718,13 @@
         <v>-5.1</v>
       </c>
       <c r="AD18" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AE18" t="n">
         <v>25</v>
       </c>
       <c r="AF18" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AG18" t="n">
         <v>25</v>
@@ -3669,7 +3736,7 @@
         <v>28</v>
       </c>
       <c r="AJ18" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AK18" t="n">
         <v>19</v>
@@ -3702,7 +3769,7 @@
         <v>28</v>
       </c>
       <c r="AU18" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AV18" t="n">
         <v>19</v>
@@ -3723,7 +3790,7 @@
         <v>20</v>
       </c>
       <c r="BB18" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BC18" t="n">
         <v>26</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>11-14-2013-14</t>
+          <t>2013-11-14</t>
         </is>
       </c>
     </row>
@@ -3833,16 +3900,16 @@
         <v>8.6</v>
       </c>
       <c r="AD19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE19" t="n">
         <v>3</v>
       </c>
       <c r="AF19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AH19" t="n">
         <v>10</v>
@@ -3878,10 +3945,10 @@
         <v>11</v>
       </c>
       <c r="AS19" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AT19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AU19" t="n">
         <v>4</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>11-14-2013-14</t>
+          <t>2013-11-14</t>
         </is>
       </c>
     </row>
@@ -4015,7 +4082,7 @@
         <v>-2</v>
       </c>
       <c r="AD20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE20" t="n">
         <v>19</v>
@@ -4033,7 +4100,7 @@
         <v>15</v>
       </c>
       <c r="AJ20" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AK20" t="n">
         <v>20</v>
@@ -4078,10 +4145,10 @@
         <v>3</v>
       </c>
       <c r="AY20" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AZ20" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BA20" t="n">
         <v>19</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>11-14-2013-14</t>
+          <t>2013-11-14</t>
         </is>
       </c>
     </row>
@@ -4119,115 +4186,115 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E21" t="n">
         <v>3</v>
       </c>
       <c r="F21" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G21" t="n">
-        <v>0.375</v>
+        <v>0.429</v>
       </c>
       <c r="H21" t="n">
         <v>48</v>
       </c>
       <c r="I21" t="n">
-        <v>36.3</v>
+        <v>36</v>
       </c>
       <c r="J21" t="n">
-        <v>84.40000000000001</v>
+        <v>84</v>
       </c>
       <c r="K21" t="n">
-        <v>0.43</v>
+        <v>0.429</v>
       </c>
       <c r="L21" t="n">
         <v>8.4</v>
       </c>
       <c r="M21" t="n">
-        <v>24.9</v>
+        <v>25.6</v>
       </c>
       <c r="N21" t="n">
-        <v>0.337</v>
+        <v>0.33</v>
       </c>
       <c r="O21" t="n">
-        <v>14</v>
+        <v>12.9</v>
       </c>
       <c r="P21" t="n">
-        <v>18.1</v>
+        <v>16.9</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.772</v>
+        <v>0.763</v>
       </c>
       <c r="R21" t="n">
         <v>10.4</v>
       </c>
       <c r="S21" t="n">
-        <v>27.3</v>
+        <v>27.4</v>
       </c>
       <c r="T21" t="n">
-        <v>37.6</v>
+        <v>37.9</v>
       </c>
       <c r="U21" t="n">
-        <v>19.4</v>
+        <v>19.3</v>
       </c>
       <c r="V21" t="n">
-        <v>13</v>
+        <v>13.6</v>
       </c>
       <c r="W21" t="n">
-        <v>8.800000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="X21" t="n">
         <v>4.9</v>
       </c>
       <c r="Y21" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="Z21" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>93.3</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>-3.6</v>
+      </c>
+      <c r="AD21" t="n">
         <v>23</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>94.90000000000001</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>-3.5</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>14</v>
       </c>
       <c r="AE21" t="n">
         <v>19</v>
       </c>
       <c r="AF21" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="AG21" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AH21" t="n">
         <v>12</v>
       </c>
       <c r="AI21" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AJ21" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AK21" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AL21" t="n">
         <v>8</v>
       </c>
       <c r="AM21" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AN21" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AO21" t="n">
         <v>29</v>
@@ -4236,7 +4303,7 @@
         <v>29</v>
       </c>
       <c r="AQ21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AR21" t="n">
         <v>21</v>
@@ -4254,22 +4321,22 @@
         <v>2</v>
       </c>
       <c r="AW21" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AX21" t="n">
         <v>18</v>
       </c>
       <c r="AY21" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AZ21" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="BA21" t="n">
         <v>29</v>
       </c>
       <c r="BB21" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="BC21" t="n">
         <v>21</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>11-14-2013-14</t>
+          <t>2013-11-14</t>
         </is>
       </c>
     </row>
@@ -4301,109 +4368,109 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E22" t="n">
         <v>5</v>
       </c>
       <c r="F22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G22" t="n">
-        <v>0.625</v>
+        <v>0.714</v>
       </c>
       <c r="H22" t="n">
-        <v>48.6</v>
+        <v>48.7</v>
       </c>
       <c r="I22" t="n">
-        <v>36.8</v>
+        <v>36.1</v>
       </c>
       <c r="J22" t="n">
-        <v>81.8</v>
+        <v>82</v>
       </c>
       <c r="K22" t="n">
-        <v>0.45</v>
+        <v>0.441</v>
       </c>
       <c r="L22" t="n">
-        <v>5.9</v>
+        <v>5.4</v>
       </c>
       <c r="M22" t="n">
-        <v>19.5</v>
+        <v>19.1</v>
       </c>
       <c r="N22" t="n">
-        <v>0.301</v>
+        <v>0.284</v>
       </c>
       <c r="O22" t="n">
-        <v>25</v>
+        <v>25.1</v>
       </c>
       <c r="P22" t="n">
-        <v>29.9</v>
+        <v>30.1</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.837</v>
+        <v>0.834</v>
       </c>
       <c r="R22" t="n">
-        <v>12.3</v>
+        <v>12.1</v>
       </c>
       <c r="S22" t="n">
-        <v>33.4</v>
+        <v>33.1</v>
       </c>
       <c r="T22" t="n">
-        <v>45.6</v>
+        <v>45.3</v>
       </c>
       <c r="U22" t="n">
         <v>20.4</v>
       </c>
       <c r="V22" t="n">
-        <v>18.1</v>
+        <v>18</v>
       </c>
       <c r="W22" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="X22" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="Y22" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="Z22" t="n">
-        <v>22.4</v>
+        <v>23.1</v>
       </c>
       <c r="AA22" t="n">
         <v>22.4</v>
       </c>
       <c r="AB22" t="n">
-        <v>104.4</v>
+        <v>102.9</v>
       </c>
       <c r="AC22" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AD22" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="AE22" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AF22" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG22" t="n">
         <v>4</v>
       </c>
-      <c r="AG22" t="n">
-        <v>7</v>
-      </c>
       <c r="AH22" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AI22" t="n">
+        <v>20</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>18</v>
+      </c>
+      <c r="AK22" t="n">
         <v>16</v>
       </c>
-      <c r="AJ22" t="n">
-        <v>19</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>15</v>
-      </c>
       <c r="AL22" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AM22" t="n">
         <v>23</v>
@@ -4424,10 +4491,10 @@
         <v>7</v>
       </c>
       <c r="AS22" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AT22" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AU22" t="n">
         <v>18</v>
@@ -4436,22 +4503,22 @@
         <v>27</v>
       </c>
       <c r="AW22" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="AX22" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AY22" t="n">
         <v>8</v>
       </c>
       <c r="AZ22" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="BA22" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BB22" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BC22" t="n">
         <v>15</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>11-14-2013-14</t>
+          <t>2013-11-14</t>
         </is>
       </c>
     </row>
@@ -4561,13 +4628,13 @@
         <v>1.1</v>
       </c>
       <c r="AD23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE23" t="n">
         <v>13</v>
       </c>
       <c r="AF23" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AG23" t="n">
         <v>16</v>
@@ -4597,16 +4664,16 @@
         <v>28</v>
       </c>
       <c r="AP23" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ23" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AR23" t="n">
         <v>14</v>
       </c>
       <c r="AS23" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AT23" t="n">
         <v>4</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>11-14-2013-14</t>
+          <t>2013-11-14</t>
         </is>
       </c>
     </row>
@@ -4743,16 +4810,16 @@
         <v>-2.8</v>
       </c>
       <c r="AD24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE24" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AF24" t="n">
         <v>12</v>
       </c>
       <c r="AG24" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AH24" t="n">
         <v>1</v>
@@ -4788,10 +4855,10 @@
         <v>18</v>
       </c>
       <c r="AS24" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AT24" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AU24" t="n">
         <v>7</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>11-14-2013-14</t>
+          <t>2013-11-14</t>
         </is>
       </c>
     </row>
@@ -4925,13 +4992,13 @@
         <v>3.6</v>
       </c>
       <c r="AD25" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AE25" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AF25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG25" t="n">
         <v>7</v>
@@ -4985,10 +5052,10 @@
         <v>4</v>
       </c>
       <c r="AX25" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AY25" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AZ25" t="n">
         <v>7</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>11-14-2013-14</t>
+          <t>2013-11-14</t>
         </is>
       </c>
     </row>
@@ -5107,7 +5174,7 @@
         <v>3.5</v>
       </c>
       <c r="AD26" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AE26" t="n">
         <v>3</v>
@@ -5143,7 +5210,7 @@
         <v>24</v>
       </c>
       <c r="AP26" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AQ26" t="n">
         <v>15</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>11-14-2013-14</t>
+          <t>2013-11-14</t>
         </is>
       </c>
     </row>
@@ -5289,13 +5356,13 @@
         <v>-3.7</v>
       </c>
       <c r="AD27" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AE27" t="n">
         <v>25</v>
       </c>
       <c r="AF27" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AG27" t="n">
         <v>25</v>
@@ -5340,7 +5407,7 @@
         <v>26</v>
       </c>
       <c r="AU27" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AV27" t="n">
         <v>1</v>
@@ -5361,7 +5428,7 @@
         <v>18</v>
       </c>
       <c r="BB27" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BC27" t="n">
         <v>22</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>11-14-2013-14</t>
+          <t>2013-11-14</t>
         </is>
       </c>
     </row>
@@ -5471,7 +5538,7 @@
         <v>9.300000000000001</v>
       </c>
       <c r="AD28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE28" t="n">
         <v>1</v>
@@ -5489,7 +5556,7 @@
         <v>3</v>
       </c>
       <c r="AJ28" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AK28" t="n">
         <v>4</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>11-14-2013-14</t>
+          <t>2013-11-14</t>
         </is>
       </c>
     </row>
@@ -5653,13 +5720,13 @@
         <v>2.4</v>
       </c>
       <c r="AD29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE29" t="n">
         <v>13</v>
       </c>
       <c r="AF29" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AG29" t="n">
         <v>16</v>
@@ -5692,7 +5759,7 @@
         <v>9</v>
       </c>
       <c r="AQ29" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AR29" t="n">
         <v>3</v>
@@ -5716,7 +5783,7 @@
         <v>25</v>
       </c>
       <c r="AY29" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AZ29" t="n">
         <v>27</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>11-14-2013-14</t>
+          <t>2013-11-14</t>
         </is>
       </c>
     </row>
@@ -5835,7 +5902,7 @@
         <v>-11.6</v>
       </c>
       <c r="AD30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE30" t="n">
         <v>30</v>
@@ -5853,7 +5920,7 @@
         <v>29</v>
       </c>
       <c r="AJ30" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AK30" t="n">
         <v>28</v>
@@ -5874,7 +5941,7 @@
         <v>6</v>
       </c>
       <c r="AQ30" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AR30" t="n">
         <v>2</v>
@@ -5883,7 +5950,7 @@
         <v>27</v>
       </c>
       <c r="AT30" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AU30" t="n">
         <v>28</v>
@@ -5901,7 +5968,7 @@
         <v>13</v>
       </c>
       <c r="AZ30" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BA30" t="n">
         <v>5</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>11-14-2013-14</t>
+          <t>2013-11-14</t>
         </is>
       </c>
     </row>
@@ -6017,7 +6084,7 @@
         <v>-4.3</v>
       </c>
       <c r="AD31" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AE31" t="n">
         <v>25</v>
@@ -6050,13 +6117,13 @@
         <v>6</v>
       </c>
       <c r="AO31" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AP31" t="n">
         <v>20</v>
       </c>
       <c r="AQ31" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AR31" t="n">
         <v>15</v>
@@ -6080,7 +6147,7 @@
         <v>24</v>
       </c>
       <c r="AY31" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AZ31" t="n">
         <v>8</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>11-14-2013-14</t>
+          <t>2013-11-14</t>
         </is>
       </c>
     </row>
